--- a/base/StructureDefinition-SGBusinessProcess.xlsx
+++ b/base/StructureDefinition-SGBusinessProcess.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -355,7 +355,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -588,7 +588,7 @@
     <t>The type of PlanDefinition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/plan-definition-type</t>
+    <t>http://hl7.org/fhir/ValueSet/plan-definition-type|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.status</t>
@@ -644,7 +644,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)</t>
+Reference(Group|4.0.1)</t>
   </si>
   <si>
     <t>Type of individual the plan definition is focused on</t>
@@ -659,7 +659,7 @@
     <t>The possible types of subjects for a plan definition (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.0.1</t>
   </si>
   <si>
     <t>Definition.subject</t>
@@ -787,7 +787,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -916,7 +916,7 @@
     <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/definition-topic|4.0.1</t>
   </si>
   <si>
     <t>Definition.subject[x]</t>
@@ -986,7 +986,7 @@
     <t>PlanDefinition.library</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Library)
+    <t xml:space="preserve">canonical(Library|4.0.1)
 </t>
   </si>
   <si>
@@ -1065,7 +1065,7 @@
     <t>Example codes for grouping goals for filtering or presentation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-category</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-category|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.description</t>
@@ -1083,7 +1083,7 @@
     <t>Describes goals that can be achieved.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.priority</t>
@@ -1098,7 +1098,7 @@
     <t>Indicates the level of importance associated with reaching or sustaining a goal.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-priority</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-priority|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.start</t>
@@ -1113,7 +1113,7 @@
     <t>Identifies the types of events that might trigger the start of a goal.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-start-event</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-start-event|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.addresses</t>
@@ -1128,7 +1128,7 @@
     <t>Identifies problems, conditions, issues, or concerns that goals may address.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.documentation</t>
@@ -1170,7 +1170,7 @@
     <t>Identifies types of parameters that can be tracked to determine goal achievement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.target.detail[x]</t>
@@ -1535,7 +1535,7 @@
     <t>Defines roles played by participants for the action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/action-participant-role|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.action.type</t>
@@ -1550,7 +1550,7 @@
     <t>The type of action to be performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-type</t>
+    <t>http://hl7.org/fhir/ValueSet/action-type|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.action.groupingBehavior</t>
@@ -1631,7 +1631,7 @@
     <t>PlanDefinition.action.definition[x]</t>
   </si>
   <si>
-    <t>canonical(ActivityDefinition|PlanDefinition|Questionnaire)
+    <t>canonical(ActivityDefinition|4.0.1|PlanDefinition|4.0.1|Questionnaire|4.0.1)
 uri</t>
   </si>
   <si>
@@ -1650,7 +1650,7 @@
     <t>PlanDefinition.action.transform</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureMap)
+    <t xml:space="preserve">canonical(StructureMap|4.0.1)
 </t>
   </si>
   <si>
@@ -2019,17 +2019,17 @@
   <dimension ref="A1:AN108"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.86328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.58984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.58984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="53.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="59.7578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2038,26 +2038,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.45703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.5625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.8203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="43.76171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.00390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="38.08984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="43.078125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="86.95703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="34.04296875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="41.19921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="77.578125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
